--- a/new-stats/besiktas-jk.xlsx
+++ b/new-stats/besiktas-jk.xlsx
@@ -1787,22 +1787,62 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Goztepe</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M24" t="n">
+        <v>12</v>
+      </c>
+      <c r="N24" t="n">
+        <v>8</v>
+      </c>
+      <c r="O24" t="n">
+        <v>7</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>

--- a/new-stats/besiktas-jk.xlsx
+++ b/new-stats/besiktas-jk.xlsx
@@ -1845,22 +1845,62 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>28/02/2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Kocaelispor</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="M25" t="n">
+        <v>11</v>
+      </c>
+      <c r="N25" t="n">
+        <v>10</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>

--- a/new-stats/besiktas-jk.xlsx
+++ b/new-stats/besiktas-jk.xlsx
@@ -1903,22 +1903,62 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>07/03/2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Galatasaray</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M26" t="n">
+        <v>24</v>
+      </c>
+      <c r="N26" t="n">
+        <v>12</v>
+      </c>
+      <c r="O26" t="n">
+        <v>7</v>
+      </c>
+      <c r="P26" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>

--- a/new-stats/besiktas-jk.xlsx
+++ b/new-stats/besiktas-jk.xlsx
@@ -1961,22 +1961,62 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Genclerbirligi</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="M27" t="n">
+        <v>24</v>
+      </c>
+      <c r="N27" t="n">
+        <v>11</v>
+      </c>
+      <c r="O27" t="n">
+        <v>7</v>
+      </c>
+      <c r="P27" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>

--- a/new-stats/besiktas-jk.xlsx
+++ b/new-stats/besiktas-jk.xlsx
@@ -2019,22 +2019,62 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>19/03/2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Kasimpasa</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M28" t="n">
+        <v>14</v>
+      </c>
+      <c r="N28" t="n">
+        <v>6</v>
+      </c>
+      <c r="O28" t="n">
+        <v>6</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
